--- a/sub_pro_12_fifa_tm_analysis/datasets/concacaf_fifa_ranking_jan_2026.xlsx
+++ b/sub_pro_12_fifa_tm_analysis/datasets/concacaf_fifa_ranking_jan_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\sports_data_sci\sub_pro_12_fifa_tm_analysis\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8246B717-7252-4723-B7CC-C4FC57C63CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75676CD4-4E1C-443D-B431-D925D33FAF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4D4A3A54-7E63-4453-BCB9-2A3BC2E3F2BC}"/>
+    <workbookView xWindow="9500" yWindow="130" windowWidth="9050" windowHeight="10070" xr2:uid="{4D4A3A54-7E63-4453-BCB9-2A3BC2E3F2BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>Bahamas</t>
   </si>
   <si>
-    <t>Countries</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -97,6 +94,9 @@
   </si>
   <si>
     <t>Ranking</t>
+  </si>
+  <si>
+    <t>Team</t>
   </si>
 </sst>
 </file>
@@ -464,295 +464,295 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>165</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2">
-        <v>165</v>
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E2" s="2">
         <v>986.58</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="2">
+        <v>206</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>206</v>
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E3" s="2">
         <v>796.6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2">
+        <v>178</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>178</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="2">
         <v>914.42</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2">
+        <v>181</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2">
-        <v>181</v>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="2">
         <v>910.74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="2">
+        <v>166</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>166</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="2">
         <v>980.49</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="2">
+        <v>183</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2">
-        <v>183</v>
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E7" s="2">
         <v>901.37</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="2">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2">
-        <v>142</v>
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E8" s="2">
         <v>1077.49</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="2">
+        <v>164</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2">
-        <v>164</v>
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E9" s="2">
         <v>989.59</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="2">
+        <v>151</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="2">
-        <v>151</v>
+      <c r="D10" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E10" s="2">
         <v>1041.9000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="2">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2">
-        <v>83</v>
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E11" s="2">
         <v>1294.49</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="2">
+        <v>70</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2">
-        <v>70</v>
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E12" s="2">
         <v>1362.4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
+      <c r="A13" s="2">
+        <v>167</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2">
-        <v>167</v>
+        <v>16</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E13" s="2">
         <v>980.28</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="2">
+        <v>154</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2">
-        <v>154</v>
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E14" s="2">
         <v>1035.25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>21</v>
+      <c r="A15" s="2">
+        <v>171</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2">
-        <v>171</v>
+        <v>16</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="2">
         <v>963.74</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="2">
+        <v>123</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="2">
-        <v>123</v>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E16" s="2">
         <v>1140.54</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="2">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2">
-        <v>97</v>
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E17" s="2">
         <v>1227.32</v>
